--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>77857</v>
+        <v>77873</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356615</v>
+        <v>113356372</v>
       </c>
       <c r="B8" t="n">
-        <v>77873</v>
+        <v>56782</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752473</v>
+        <v>752505</v>
       </c>
       <c r="R8" t="n">
-        <v>7194715</v>
+        <v>7194699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,6 +1471,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356372</v>
+        <v>113356615</v>
       </c>
       <c r="B9" t="n">
-        <v>56781</v>
+        <v>77885</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,21 +1522,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752505</v>
+        <v>752473</v>
       </c>
       <c r="R9" t="n">
-        <v>7194699</v>
+        <v>7194715</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,11 +1582,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356372</v>
+        <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>56782</v>
+        <v>77885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752505</v>
+        <v>752473</v>
       </c>
       <c r="R8" t="n">
-        <v>7194699</v>
+        <v>7194715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,11 +1471,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356615</v>
+        <v>113356372</v>
       </c>
       <c r="B9" t="n">
-        <v>77885</v>
+        <v>56782</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,21 +1517,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752473</v>
+        <v>752505</v>
       </c>
       <c r="R9" t="n">
-        <v>7194715</v>
+        <v>7194699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,6 +1577,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>77885</v>
+        <v>77907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>77907</v>
+        <v>77910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>113356372</v>
       </c>
       <c r="B9" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356615</v>
+        <v>113356372</v>
       </c>
       <c r="B8" t="n">
-        <v>77910</v>
+        <v>56789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752473</v>
+        <v>752505</v>
       </c>
       <c r="R8" t="n">
-        <v>7194715</v>
+        <v>7194699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,6 +1471,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356372</v>
+        <v>113356615</v>
       </c>
       <c r="B9" t="n">
-        <v>56785</v>
+        <v>77916</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,21 +1522,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752505</v>
+        <v>752473</v>
       </c>
       <c r="R9" t="n">
-        <v>7194699</v>
+        <v>7194715</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,11 +1582,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356372</v>
+        <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>56789</v>
+        <v>77916</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752505</v>
+        <v>752473</v>
       </c>
       <c r="R8" t="n">
-        <v>7194699</v>
+        <v>7194715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,11 +1471,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356615</v>
+        <v>113356372</v>
       </c>
       <c r="B9" t="n">
-        <v>77916</v>
+        <v>56789</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,21 +1517,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752473</v>
+        <v>752505</v>
       </c>
       <c r="R9" t="n">
-        <v>7194715</v>
+        <v>7194699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,6 +1577,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356615</v>
+        <v>113356372</v>
       </c>
       <c r="B8" t="n">
-        <v>77916</v>
+        <v>56796</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752473</v>
+        <v>752505</v>
       </c>
       <c r="R8" t="n">
-        <v>7194715</v>
+        <v>7194699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,6 +1471,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356372</v>
+        <v>113356615</v>
       </c>
       <c r="B9" t="n">
-        <v>56789</v>
+        <v>77923</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,21 +1522,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752505</v>
+        <v>752473</v>
       </c>
       <c r="R9" t="n">
-        <v>7194699</v>
+        <v>7194715</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,11 +1582,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356372</v>
+        <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>56796</v>
+        <v>77925</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752505</v>
+        <v>752473</v>
       </c>
       <c r="R8" t="n">
-        <v>7194699</v>
+        <v>7194715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,11 +1471,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356615</v>
+        <v>113356372</v>
       </c>
       <c r="B9" t="n">
-        <v>77923</v>
+        <v>56798</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,21 +1517,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752473</v>
+        <v>752505</v>
       </c>
       <c r="R9" t="n">
-        <v>7194715</v>
+        <v>7194699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,6 +1577,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>77925</v>
+        <v>77953</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>113356372</v>
       </c>
       <c r="B9" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,69 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15703810</v>
+        <v>63564562</v>
       </c>
       <c r="B2" t="n">
-        <v>6207</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101905</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordlig flatbagge</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thymalus oblongus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reitter, 1889</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Aftonmyrberget, Vb</t>
+          <t>Norsjömorberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752501.0575933922</v>
+        <v>752258</v>
       </c>
       <c r="R2" t="n">
-        <v>7194693.483357338</v>
+        <v>7194732</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,22 +746,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-06-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,26 +763,15 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Citronticka på tallåga</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Nils Ericson</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nils Ericson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nils Ericson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -820,12 +781,7 @@
         <v>63564570</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -863,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752311.2453853642</v>
+        <v>752311</v>
       </c>
       <c r="R3" t="n">
-        <v>7194731.916422088</v>
+        <v>7194732</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -896,19 +852,9 @@
           <t>2011-05-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-05-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63564562</v>
+        <v>63564575</v>
       </c>
       <c r="B4" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752258.4665892241</v>
+        <v>752296</v>
       </c>
       <c r="R4" t="n">
-        <v>7194732.189448072</v>
+        <v>7194713</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,19 +955,9 @@
           <t>2011-05-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-05-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,37 +984,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63564575</v>
+        <v>63564590</v>
       </c>
       <c r="B5" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1099,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752295.7122749418</v>
+        <v>752458</v>
       </c>
       <c r="R5" t="n">
-        <v>7194712.61759275</v>
+        <v>7194844</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1132,19 +1058,9 @@
           <t>2011-05-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-05-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,15 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88556946</v>
+        <v>63564599</v>
       </c>
       <c r="B6" t="n">
-        <v>6207</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,37 +1098,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101905</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordlig flatbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thymalus oblongus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reitter, 1889</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aftonmyrberget, Vb</t>
+          <t>Norsjömorberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752506.912795832</v>
+        <v>752539</v>
       </c>
       <c r="R6" t="n">
-        <v>7194695.261445105</v>
+        <v>7194691</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,22 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,27 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulf Sperens, Nils Ericson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88556947</v>
+        <v>113356615</v>
       </c>
       <c r="B7" t="n">
-        <v>6211</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100524</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aftonmyrberget, Vb</t>
+          <t>Boliden, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752506.912795832</v>
+        <v>752473</v>
       </c>
       <c r="R7" t="n">
-        <v>7194695.261445105</v>
+        <v>7194715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,22 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,27 +1275,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Johanna Kühne</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulf Sperens, Nils Ericson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Johanna Kühne, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356615</v>
+        <v>113356617</v>
       </c>
       <c r="B8" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752473</v>
+        <v>752479</v>
       </c>
       <c r="R8" t="n">
-        <v>7194715</v>
+        <v>7194717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,37 +1392,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356617</v>
+        <v>113356372</v>
       </c>
       <c r="B9" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752479</v>
+        <v>752505</v>
       </c>
       <c r="R9" t="n">
-        <v>7194717</v>
+        <v>7194698</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,15 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113356372</v>
+        <v>88556947</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>6284</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,34 +1509,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100524</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Thunberg, 1784)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Boliden, Vb</t>
+          <t>Aftonmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752505</v>
+        <v>752507</v>
       </c>
       <c r="R10" t="n">
-        <v>7194698</v>
+        <v>7194695</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,17 +1563,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2012-06-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>2012-06-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,19 +1583,239 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johanna Kühne</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Ulf Sperens, Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15703810</v>
+      </c>
+      <c r="B11" t="n">
+        <v>6279</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101905</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nordlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Thymalus oblongus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Reitter, 1889</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Aftonmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>752501</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7194693</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2012-06-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2012-06-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Citronticka på tallåga</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>88556946</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6279</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101905</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nordlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Thymalus oblongus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Reitter, 1889</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Aftonmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>752507</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7194695</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulf Sperens, Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,54 +984,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63564590</v>
+        <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>91896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norsjömorberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752458</v>
+        <v>752485</v>
       </c>
       <c r="R5" t="n">
-        <v>7194844</v>
+        <v>7194777</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1049,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-05-13</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-05-13</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,19 +1079,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63564599</v>
+        <v>63564590</v>
       </c>
       <c r="B6" t="n">
         <v>79327</v>
@@ -1128,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752539</v>
+        <v>752458</v>
       </c>
       <c r="R6" t="n">
-        <v>7194691</v>
+        <v>7194844</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1190,48 +1194,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356615</v>
+        <v>63564599</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Boliden, Vb</t>
+          <t>Norsjömorberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752473</v>
+        <v>752539</v>
       </c>
       <c r="R7" t="n">
-        <v>7194715</v>
+        <v>7194691</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2011-05-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2011-05-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,23 +1285,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johanna Kühne</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356617</v>
+        <v>113356615</v>
       </c>
       <c r="B8" t="n">
         <v>79084</v>
@@ -1326,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752479</v>
+        <v>752473</v>
       </c>
       <c r="R8" t="n">
-        <v>7194717</v>
+        <v>7194715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356372</v>
+        <v>113356617</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752505</v>
+        <v>752479</v>
       </c>
       <c r="R9" t="n">
-        <v>7194698</v>
+        <v>7194717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,11 +1469,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88556947</v>
+        <v>135531215</v>
       </c>
       <c r="B10" t="n">
-        <v>6284</v>
+        <v>78377</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1509,34 +1510,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100524</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aftonmyrberget, Vb</t>
+          <t>Norsjömorberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752507</v>
+        <v>752504</v>
       </c>
       <c r="R10" t="n">
-        <v>7194695</v>
+        <v>7194775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,12 +1564,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,79 +1594,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulf Sperens, Nils Ericson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15703810</v>
+        <v>113356372</v>
       </c>
       <c r="B11" t="n">
-        <v>6279</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101905</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordlig flatbagge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymalus oblongus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reitter, 1889</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aftonmyrberget, Vb</t>
+          <t>Boliden, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>752501</v>
+        <v>752505</v>
       </c>
       <c r="R11" t="n">
-        <v>7194693</v>
+        <v>7194698</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,12 +1671,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2012-06-13</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2012-06-13</t>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1696,58 +1693,51 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Citronticka på tallåga</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>Nils Ericson</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nils Ericson</t>
+          <t>Johanna Kühne</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nils Ericson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Johanna Kühne, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>88556946</v>
+        <v>88556947</v>
       </c>
       <c r="B12" t="n">
-        <v>6279</v>
+        <v>6284</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101905</v>
+        <v>100524</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordlig flatbagge</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymalus oblongus</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Reitter, 1889</t>
+          <t>(Thunberg, 1784)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,6 +1806,799 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>15703810</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6279</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101905</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nordlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thymalus oblongus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Reitter, 1889</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Aftonmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>752501</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7194693</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2012-06-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2012-06-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Citronticka på tallåga</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>88556946</v>
+      </c>
+      <c r="B14" t="n">
+        <v>6279</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101905</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nordlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Thymalus oblongus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Reitter, 1889</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Aftonmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>752507</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7194695</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulf Sperens, Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135531209</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norsjömorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>752429</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7194837</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Läte</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135531210</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norsjömorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>752456</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7194828</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Läten, flera individer</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135531212</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norsjömorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>752472</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7194780</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135531211</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norsjömorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>752452</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7194792</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I blom bild</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135531227</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norsjömorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>752404</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7194855</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63564562</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63564570</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63564575</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531213</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63564590</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63564599</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356615</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356617</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531215</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1709,6 +1759,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356372</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,6 +1861,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88556947</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1933,6 +1993,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15703810</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2030,6 +2095,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88556946</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2147,6 +2217,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531209</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2264,6 +2339,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531210</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2371,6 +2451,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531212</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2492,6 +2577,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531211</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2599,8 +2689,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531227</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>135531215</v>
       </c>
       <c r="B10" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>135531209</v>
       </c>
       <c r="B15" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>135531210</v>
       </c>
       <c r="B16" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>135531212</v>
       </c>
       <c r="B17" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>135531215</v>
       </c>
       <c r="B10" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1004,54 +1004,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63564590</v>
+        <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norsjömorberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752458</v>
+        <v>752485</v>
       </c>
       <c r="R5" t="n">
-        <v>7194844</v>
+        <v>7194777</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,12 +1069,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-05-13</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-05-13</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,24 +1099,28 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63564590</t>
+          <t>https://artportalen.se/Sighting/135531213</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63564599</v>
+        <v>63564590</v>
       </c>
       <c r="B6" t="n">
         <v>79327</v>
@@ -1153,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752539</v>
+        <v>752458</v>
       </c>
       <c r="R6" t="n">
-        <v>7194691</v>
+        <v>7194844</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,54 +1222,60 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63564599</t>
+          <t>https://artportalen.se/Sighting/63564590</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356615</v>
+        <v>63564599</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Boliden, Vb</t>
+          <t>Norsjömorberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752473</v>
+        <v>752539</v>
       </c>
       <c r="R7" t="n">
-        <v>7194715</v>
+        <v>7194691</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,12 +1299,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2011-05-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2011-05-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,28 +1319,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johanna Kühne</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113356615</t>
+          <t>https://artportalen.se/Sighting/63564599</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356617</v>
+        <v>113356615</v>
       </c>
       <c r="B8" t="n">
         <v>79084</v>
@@ -1361,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752479</v>
+        <v>752473</v>
       </c>
       <c r="R8" t="n">
-        <v>7194717</v>
+        <v>7194715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,38 +1436,38 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113356617</t>
+          <t>https://artportalen.se/Sighting/113356615</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356372</v>
+        <v>113356617</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752505</v>
+        <v>752479</v>
       </c>
       <c r="R9" t="n">
-        <v>7194698</v>
+        <v>7194717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,11 +1515,6 @@
           <t>2023-08-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1537,16 +1542,16 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113356372</t>
+          <t>https://artportalen.se/Sighting/113356617</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88556947</v>
+        <v>135531215</v>
       </c>
       <c r="B10" t="n">
-        <v>6284</v>
+        <v>78445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,34 +1559,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100524</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aftonmyrberget, Vb</t>
+          <t>Norsjömorberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752507</v>
+        <v>752504</v>
       </c>
       <c r="R10" t="n">
-        <v>7194695</v>
+        <v>7194775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,12 +1613,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,84 +1643,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulf Sperens, Nils Ericson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88556947</t>
+          <t>https://artportalen.se/Sighting/135531215</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15703810</v>
+        <v>113356372</v>
       </c>
       <c r="B11" t="n">
-        <v>6279</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101905</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordlig flatbagge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymalus oblongus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reitter, 1889</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aftonmyrberget, Vb</t>
+          <t>Boliden, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>752501</v>
+        <v>752505</v>
       </c>
       <c r="R11" t="n">
-        <v>7194693</v>
+        <v>7194698</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,12 +1729,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2012-06-13</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2012-06-13</t>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,63 +1751,56 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Citronticka på tallåga</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>Nils Ericson</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nils Ericson</t>
+          <t>Johanna Kühne</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nils Ericson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Johanna Kühne, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15703810</t>
+          <t>https://artportalen.se/Sighting/113356372</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>88556946</v>
+        <v>88556947</v>
       </c>
       <c r="B12" t="n">
-        <v>6279</v>
+        <v>6284</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101905</v>
+        <v>100524</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordlig flatbagge</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymalus oblongus</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Reitter, 1889</t>
+          <t>(Thunberg, 1784)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1873,7 +1871,855 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/88556947</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>15703810</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6279</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101905</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nordlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thymalus oblongus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Reitter, 1889</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Aftonmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>752501</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7194693</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2012-06-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2012-06-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Citronticka på tallåga</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15703810</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>88556946</v>
+      </c>
+      <c r="B14" t="n">
+        <v>6279</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101905</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nordlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Thymalus oblongus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Reitter, 1889</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Aftonmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>752507</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7194695</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulf Sperens, Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/88556946</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135531209</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norsjömorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>752429</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7194837</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Läte</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531209</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135531210</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norsjömorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>752456</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7194828</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Läten, flera individer</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531210</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135531212</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norsjömorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>752472</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7194780</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531212</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135531211</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norsjömorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>752452</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7194792</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I blom bild</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531211</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135531227</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norsjömorberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>752404</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7194855</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531227</t>
         </is>
       </c>
     </row>
@@ -1890,6 +2736,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>135531215</v>
       </c>
       <c r="B10" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>135531209</v>
       </c>
       <c r="B15" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>135531210</v>
       </c>
       <c r="B16" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>135531212</v>
       </c>
       <c r="B17" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>135531215</v>
       </c>
       <c r="B10" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>135531215</v>
       </c>
       <c r="B10" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>135531209</v>
       </c>
       <c r="B15" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>135531210</v>
       </c>
       <c r="B16" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>135531212</v>
       </c>
       <c r="B17" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>135531215</v>
       </c>
       <c r="B10" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>135531209</v>
       </c>
       <c r="B15" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>135531210</v>
       </c>
       <c r="B16" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>135531212</v>
       </c>
       <c r="B17" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>135531215</v>
       </c>
       <c r="B10" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>135531209</v>
       </c>
       <c r="B15" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>135531210</v>
       </c>
       <c r="B16" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>135531212</v>
       </c>
       <c r="B17" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>135531215</v>
       </c>
       <c r="B10" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>135531215</v>
       </c>
       <c r="B10" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>135531209</v>
       </c>
       <c r="B15" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>135531210</v>
       </c>
       <c r="B16" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>135531212</v>
       </c>
       <c r="B17" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11867-2022 artfynd.xlsx
+++ b/artfynd/A 11867-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>135531213</v>
       </c>
       <c r="B5" t="n">
-        <v>92009</v>
+        <v>92010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135531211</v>
       </c>
       <c r="B18" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>135531227</v>
       </c>
       <c r="B19" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
